--- a/output/pdf_financials_xlsx/SDI.xlsx
+++ b/output/pdf_financials_xlsx/SDI.xlsx
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>0.884</v>
@@ -10758,7 +10758,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>0.06</v>
       </c>

--- a/output/pdf_financials_xlsx/SDI.xlsx
+++ b/output/pdf_financials_xlsx/SDI.xlsx
@@ -1666,19 +1666,19 @@
         <v>0.321</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.665</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.703</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.517</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.756</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="35">
@@ -1740,19 +1740,19 @@
         <v>0.321</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.665</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.703</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.517</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.756</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="37">
@@ -2184,19 +2184,19 @@
         <v>0.123</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.878</v>
+        <v>0.213</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.018</v>
+        <v>0.315</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.804</v>
+        <v>0.287</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.155</v>
+        <v>0.399</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.031</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="49">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/SDI.xlsx
+++ b/output/pdf_financials_xlsx/SDI.xlsx
@@ -20714,7 +20714,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -21042,7 +21046,11 @@
           <t>Depreciation of right-of-use assets 4</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -25688,7 +25696,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -25816,7 +25828,11 @@
           <t>Depreciation of right-of-use assets 7</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SDI.xlsx
+++ b/output/pdf_financials_xlsx/SDI.xlsx
@@ -1164,10 +1164,10 @@
         <v>-6.875</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.079</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-1.252</v>
+        <v>-1.247</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>2.852</v>
@@ -1201,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-4.036</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>1.002</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>4.365</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -3018,19 +3018,19 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.433</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="71">
@@ -3055,19 +3055,19 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.433</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="72">
@@ -3203,19 +3203,19 @@
         <v>11.253</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>7.602</v>
+        <v>7.445</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>12.101</v>
+        <v>11.668</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2.851</v>
+        <v>2.43</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>4.178</v>
+        <v>3.796</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>7.793</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="76">
@@ -3398,19 +3398,19 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.006467840459935321</v>
+        <v>0.01080737444373808</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.01787784956101788</v>
+        <v>0.0233953897320234</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.01115186921178362</v>
+        <v>0.01591830265154088</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.001139846228291844</v>
+        <v>0.005247593956664337</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.01291239278565428</v>
+        <v>0.01906263288356029</v>
       </c>
     </row>
     <row r="81">
@@ -4065,10 +4065,10 @@
         <v>-6.875</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-4.124</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-0.245</v>
+        <v>-1.247</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>2.852</v>
@@ -6328,7 +6328,11 @@
           <t>Lease liabilities 5, 20</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -7762,7 +7766,11 @@
           <t>Lease liabilities 5</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -11344,7 +11352,11 @@
           <t>Deferred income tax expense 19</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -15410,7 +15422,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -15862,7 +15878,11 @@
           <t>Deferred tax recovery 20</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -17808,7 +17828,11 @@
           <t>Deferred income tax recovery 17</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -19460,7 +19484,11 @@
           <t>Net Income (loss)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E218" s="5" t="n">
         <v>-1.795</v>
       </c>
@@ -19852,7 +19880,11 @@
           <t>Deferred tax expense (recovery) 14</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E224" s="5" t="n">
         <v>-0.1</v>
       </c>
@@ -26212,7 +26244,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -26278,7 +26314,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
